--- a/ForHome8/DataScience/data_audit_task02.xlsx
+++ b/ForHome8/DataScience/data_audit_task02.xlsx
@@ -126,7 +126,7 @@
     <font>
       <sz val="12"/>
       <name val="Times New Roman"/>
-      <family val="1"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -210,9 +210,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>177120</xdr:colOff>
+      <xdr:colOff>176760</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>5437800</xdr:rowOff>
+      <xdr:rowOff>5437440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -226,7 +226,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="1694880"/>
-          <a:ext cx="6391080" cy="5266800"/>
+          <a:ext cx="6390720" cy="5266440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -247,9 +247,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>89640</xdr:colOff>
+      <xdr:colOff>89280</xdr:colOff>
       <xdr:row>96</xdr:row>
-      <xdr:rowOff>12240</xdr:rowOff>
+      <xdr:rowOff>11880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -263,7 +263,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="8061120"/>
-          <a:ext cx="16382520" cy="16392240"/>
+          <a:ext cx="16394040" cy="16391880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -284,9 +284,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>654480</xdr:colOff>
+      <xdr:colOff>654120</xdr:colOff>
       <xdr:row>124</xdr:row>
-      <xdr:rowOff>100440</xdr:rowOff>
+      <xdr:rowOff>100080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -300,7 +300,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1581120" y="24846840"/>
-          <a:ext cx="6143400" cy="5028840"/>
+          <a:ext cx="6143040" cy="5028480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -321,9 +321,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>359640</xdr:colOff>
+      <xdr:colOff>359280</xdr:colOff>
       <xdr:row>122</xdr:row>
-      <xdr:rowOff>148680</xdr:rowOff>
+      <xdr:rowOff>148320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -337,7 +337,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8359560" y="24780600"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:ext cx="6676560" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -358,9 +358,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>549720</xdr:colOff>
+      <xdr:colOff>549360</xdr:colOff>
       <xdr:row>148</xdr:row>
-      <xdr:rowOff>127080</xdr:rowOff>
+      <xdr:rowOff>126720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -374,7 +374,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="1581120" y="29998080"/>
-          <a:ext cx="6038640" cy="4476240"/>
+          <a:ext cx="6038280" cy="4475880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -395,9 +395,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>501480</xdr:colOff>
+      <xdr:colOff>501120</xdr:colOff>
       <xdr:row>149</xdr:row>
-      <xdr:rowOff>55080</xdr:rowOff>
+      <xdr:rowOff>54720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -411,7 +411,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="8501400" y="29830680"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:ext cx="6676560" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -432,9 +432,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>423360</xdr:colOff>
+      <xdr:colOff>423000</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>6163920</xdr:rowOff>
+      <xdr:rowOff>6163560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -443,8 +443,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9066240" y="1894320"/>
-          <a:ext cx="5211720" cy="5793480"/>
+          <a:off x="9066960" y="1894320"/>
+          <a:ext cx="5218560" cy="5793120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -469,7 +469,11 @@
           <a:noAutofit/>
         </a:bodyPr>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Times New Roman"/>
@@ -481,19 +485,31 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
             <a:latin typeface="Times New Roman"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:endParaRPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
             <a:latin typeface="Times New Roman"/>
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Times New Roman"/>
@@ -512,7 +528,11 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Times New Roman"/>
@@ -524,7 +544,11 @@
           </a:endParaRPr>
         </a:p>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr algn="ctr">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+          </a:pPr>
           <a:r>
             <a:rPr b="0" lang="en-US" sz="1200" spc="-1" strike="noStrike">
               <a:latin typeface="Times New Roman"/>
@@ -553,9 +577,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273960</xdr:colOff>
+      <xdr:colOff>273600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>189720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -568,8 +592,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1836360" y="0"/>
-          <a:ext cx="7619760" cy="5714640"/>
+          <a:off x="1838160" y="0"/>
+          <a:ext cx="7626960" cy="5714280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -595,9 +619,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273960</xdr:colOff>
+      <xdr:colOff>273600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>189720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -610,8 +634,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1836360" y="0"/>
-          <a:ext cx="7619760" cy="5714640"/>
+          <a:off x="1838160" y="0"/>
+          <a:ext cx="7626960" cy="5714280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -637,9 +661,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273960</xdr:colOff>
+      <xdr:colOff>273600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>189720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -652,8 +676,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1836360" y="0"/>
-          <a:ext cx="7619760" cy="5714640"/>
+          <a:off x="1838160" y="0"/>
+          <a:ext cx="7626960" cy="5714280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -679,9 +703,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273960</xdr:colOff>
+      <xdr:colOff>273600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>189720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -694,8 +718,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1836360" y="0"/>
-          <a:ext cx="7619760" cy="5714640"/>
+          <a:off x="1838160" y="0"/>
+          <a:ext cx="7626960" cy="5714280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -721,9 +745,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273960</xdr:colOff>
+      <xdr:colOff>273600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>189720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -736,8 +760,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1836360" y="0"/>
-          <a:ext cx="7619760" cy="5714640"/>
+          <a:off x="1838160" y="0"/>
+          <a:ext cx="7626960" cy="5714280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -763,9 +787,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273960</xdr:colOff>
+      <xdr:colOff>273600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>189720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -778,8 +802,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1836360" y="0"/>
-          <a:ext cx="7619760" cy="5714640"/>
+          <a:off x="1838160" y="0"/>
+          <a:ext cx="7626960" cy="5714280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -805,9 +829,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>273960</xdr:colOff>
+      <xdr:colOff>273600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>190080</xdr:rowOff>
+      <xdr:rowOff>189720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -820,8 +844,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1836360" y="0"/>
-          <a:ext cx="7619760" cy="5714640"/>
+          <a:off x="1838160" y="0"/>
+          <a:ext cx="7626960" cy="5714280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -842,7 +866,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.55078125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.41"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.98"/>
@@ -1199,7 +1223,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B171"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -2587,7 +2611,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B187"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -4103,7 +4127,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B189"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -5635,7 +5659,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B185"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -7135,7 +7159,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B208"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -8819,7 +8843,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B149"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -10031,7 +10055,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
